--- a/scripts/python/sf-doc-mcp/機能一覧テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/機能一覧テンプレート.xlsx
@@ -1904,25 +1904,20 @@
       <c r="X7" s="3" t="n"/>
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="6" t="inlineStr">
-        <is>
-          <t>設計書ファイル</t>
-        </is>
-      </c>
+      <c r="AA7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
       <c r="AC7" s="3" t="n"/>
       <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="S7:AA7"/>
+    <mergeCell ref="S7:AE7"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="B6:AE6"/>
-    <mergeCell ref="AB7:AE7"/>
     <mergeCell ref="F4:R4"/>
     <mergeCell ref="W3:AE3"/>
     <mergeCell ref="B3:E3"/>

--- a/scripts/python/sf-doc-mcp/機能一覧テンプレート.xlsx
+++ b/scripts/python/sf-doc-mcp/機能一覧テンプレート.xlsx
@@ -1613,25 +1613,29 @@
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>バージョン</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="4" t="n"/>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>合計件数</t>
-        </is>
-      </c>
+      <c r="P4" s="4" t="n"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="4" t="n"/>
-      <c r="W4" s="5" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>合計件数</t>
+        </is>
+      </c>
       <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="3" t="n"/>
-      <c r="Z4" s="3" t="n"/>
+      <c r="Y4" s="4" t="n"/>
+      <c r="Z4" s="5" t="inlineStr"/>
       <c r="AA4" s="3" t="n"/>
       <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="n"/>
@@ -1695,20 +1699,22 @@
       <c r="AE7" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="B1:AE1"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="S4:V4"/>
+    <mergeCell ref="M4:P4"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:AE6"/>
     <mergeCell ref="D7:K7"/>
-    <mergeCell ref="F4:R4"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="Q4:V4"/>
     <mergeCell ref="W3:AE3"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="W4:Y4"/>
     <mergeCell ref="F3:R3"/>
     <mergeCell ref="L7:O7"/>
-    <mergeCell ref="W4:AE4"/>
+    <mergeCell ref="Z4:AE4"/>
     <mergeCell ref="P7:AE7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1721,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AE7"/>
+  <dimension ref="B1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1765,86 +1771,52 @@
       </c>
     </row>
     <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="22" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>プロジェクト名</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="5">
-        <f>サマリー!G3</f>
-        <v/>
-      </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>作成日</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="n"/>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="5">
-        <f>サマリー!W3</f>
-        <v/>
-      </c>
-      <c r="X3" s="3" t="n"/>
-      <c r="Y3" s="3" t="n"/>
-      <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="3" t="n"/>
-      <c r="AB3" s="3" t="n"/>
-      <c r="AC3" s="3" t="n"/>
-      <c r="AD3" s="3" t="n"/>
-      <c r="AE3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>作成者</t>
+    <row r="3" ht="26" customHeight="1">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>■ 機能一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="5">
-        <f>サマリー!G4</f>
-        <v/>
-      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>API名/ファイル名</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>機能名</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="4" t="n"/>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>件数</t>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>処理概要</t>
         </is>
       </c>
       <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="5" t="inlineStr"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
       <c r="X4" s="3" t="n"/>
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
@@ -1854,78 +1826,14 @@
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="4" t="n"/>
     </row>
-    <row r="5" ht="12" customHeight="1"/>
-    <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>■ 機能一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>API名/ファイル名</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>機能名</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
-      <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>処理概要</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="n"/>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="3" t="n"/>
-      <c r="AC7" s="3" t="n"/>
-      <c r="AD7" s="3" t="n"/>
-      <c r="AE7" s="4" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="6">
     <mergeCell ref="B1:AE1"/>
-    <mergeCell ref="S7:AE7"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="S4:V4"/>
-    <mergeCell ref="B6:AE6"/>
-    <mergeCell ref="F4:R4"/>
-    <mergeCell ref="W3:AE3"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="L7:R7"/>
-    <mergeCell ref="F3:R3"/>
-    <mergeCell ref="E7:K7"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="W4:AE4"/>
+    <mergeCell ref="S4:AE4"/>
+    <mergeCell ref="L4:R4"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="B3:AE3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
